--- a/artfynd/A 68737-2019 artfynd.xlsx
+++ b/artfynd/A 68737-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121410044</v>
       </c>
       <c r="B2" t="n">
-        <v>94494</v>
+        <v>94506</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121410040</v>
+        <v>121410034</v>
       </c>
       <c r="B3" t="n">
-        <v>94494</v>
+        <v>57367</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,31 +794,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -870,7 +874,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -889,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121410035</v>
+        <v>121410040</v>
       </c>
       <c r="B4" t="n">
-        <v>74520</v>
+        <v>94506</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,26 +908,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6428</v>
+        <v>2810</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -995,10 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121410034</v>
+        <v>121410035</v>
       </c>
       <c r="B5" t="n">
-        <v>57367</v>
+        <v>74522</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,35 +1011,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6428</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1087,6 +1086,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 68737-2019 artfynd.xlsx
+++ b/artfynd/A 68737-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121410044</v>
       </c>
       <c r="B2" t="n">
-        <v>94506</v>
+        <v>94507</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121410034</v>
+        <v>121410035</v>
       </c>
       <c r="B3" t="n">
-        <v>57367</v>
+        <v>74522</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,35 +794,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6428</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -874,6 +869,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -892,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121410040</v>
+        <v>121410034</v>
       </c>
       <c r="B4" t="n">
-        <v>94506</v>
+        <v>57367</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,31 +900,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -980,7 +980,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -999,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121410035</v>
+        <v>121410040</v>
       </c>
       <c r="B5" t="n">
-        <v>74522</v>
+        <v>94507</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1015,26 +1014,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6428</v>
+        <v>2810</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>

--- a/artfynd/A 68737-2019 artfynd.xlsx
+++ b/artfynd/A 68737-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121410044</v>
       </c>
       <c r="B2" t="n">
-        <v>94507</v>
+        <v>94510</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>121410035</v>
       </c>
       <c r="B3" t="n">
-        <v>74522</v>
+        <v>74525</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>121410034</v>
       </c>
       <c r="B4" t="n">
-        <v>57367</v>
+        <v>57370</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>121410040</v>
       </c>
       <c r="B5" t="n">
-        <v>94507</v>
+        <v>94510</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 68737-2019 artfynd.xlsx
+++ b/artfynd/A 68737-2019 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121410035</v>
+        <v>121410040</v>
       </c>
       <c r="B3" t="n">
-        <v>74525</v>
+        <v>94510</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,26 +798,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6428</v>
+        <v>2810</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -888,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121410034</v>
+        <v>121410035</v>
       </c>
       <c r="B4" t="n">
-        <v>57370</v>
+        <v>74525</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,35 +901,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6428</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -980,6 +976,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -998,10 +995,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121410040</v>
+        <v>121410034</v>
       </c>
       <c r="B5" t="n">
-        <v>94510</v>
+        <v>57370</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1010,31 +1007,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1086,7 +1087,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 68737-2019 artfynd.xlsx
+++ b/artfynd/A 68737-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121410044</v>
       </c>
       <c r="B2" t="n">
-        <v>94510</v>
+        <v>94516</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121410040</v>
+        <v>121410034</v>
       </c>
       <c r="B3" t="n">
-        <v>94510</v>
+        <v>57371</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,31 +794,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -870,7 +874,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -892,7 +895,7 @@
         <v>121410035</v>
       </c>
       <c r="B4" t="n">
-        <v>74525</v>
+        <v>74526</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -995,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121410034</v>
+        <v>121410040</v>
       </c>
       <c r="B5" t="n">
-        <v>57370</v>
+        <v>94516</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,35 +1010,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1087,6 +1086,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 68737-2019 artfynd.xlsx
+++ b/artfynd/A 68737-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121410044</v>
       </c>
       <c r="B2" t="n">
-        <v>94516</v>
+        <v>94517</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121410034</v>
+        <v>121410035</v>
       </c>
       <c r="B3" t="n">
-        <v>57371</v>
+        <v>74527</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,35 +794,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6428</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -874,6 +869,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -892,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121410035</v>
+        <v>121410040</v>
       </c>
       <c r="B4" t="n">
-        <v>74526</v>
+        <v>94517</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,26 +904,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6428</v>
+        <v>2810</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -998,10 +995,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121410040</v>
+        <v>121410034</v>
       </c>
       <c r="B5" t="n">
-        <v>94516</v>
+        <v>57372</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1010,31 +1007,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1086,7 +1087,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 68737-2019 artfynd.xlsx
+++ b/artfynd/A 68737-2019 artfynd.xlsx
@@ -888,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121410040</v>
+        <v>121410034</v>
       </c>
       <c r="B4" t="n">
-        <v>94517</v>
+        <v>57372</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,31 +900,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -976,7 +980,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -995,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121410034</v>
+        <v>121410040</v>
       </c>
       <c r="B5" t="n">
-        <v>57372</v>
+        <v>94517</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,35 +1010,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1087,6 +1086,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 68737-2019 artfynd.xlsx
+++ b/artfynd/A 68737-2019 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121410035</v>
+        <v>121410034</v>
       </c>
       <c r="B3" t="n">
-        <v>74527</v>
+        <v>57372</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,30 +794,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6428</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -869,7 +874,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -888,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121410034</v>
+        <v>121410040</v>
       </c>
       <c r="B4" t="n">
-        <v>57372</v>
+        <v>94517</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,35 +904,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -980,6 +980,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -998,10 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121410040</v>
+        <v>121410035</v>
       </c>
       <c r="B5" t="n">
-        <v>94517</v>
+        <v>74527</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1014,27 +1015,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2810</v>
+        <v>6428</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>

--- a/artfynd/A 68737-2019 artfynd.xlsx
+++ b/artfynd/A 68737-2019 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121410034</v>
+        <v>121410035</v>
       </c>
       <c r="B3" t="n">
-        <v>57372</v>
+        <v>74527</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,35 +794,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6428</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -874,6 +869,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -999,10 +995,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121410035</v>
+        <v>121410034</v>
       </c>
       <c r="B5" t="n">
-        <v>74527</v>
+        <v>57372</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1011,30 +1007,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6428</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1086,7 +1087,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 68737-2019 artfynd.xlsx
+++ b/artfynd/A 68737-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121410044</v>
       </c>
       <c r="B2" t="n">
-        <v>94517</v>
+        <v>94525</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121410035</v>
+        <v>121410040</v>
       </c>
       <c r="B3" t="n">
-        <v>74527</v>
+        <v>94525</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,26 +798,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6428</v>
+        <v>2810</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -888,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121410040</v>
+        <v>121410034</v>
       </c>
       <c r="B4" t="n">
-        <v>94517</v>
+        <v>57373</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,31 +901,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -976,7 +981,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -995,10 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121410034</v>
+        <v>121410035</v>
       </c>
       <c r="B5" t="n">
-        <v>57372</v>
+        <v>74534</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,35 +1011,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6428</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1087,6 +1086,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
